--- a/forms/trg/Formulir_TRG_nap.xlsx
+++ b/forms/trg/Formulir_TRG_nap.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B28)</f>
+        <f>COUNTA(Anggota!B5:B29)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F28)</f>
+        <f>COUNTA(Anggota!F5:F29)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ir. Nurul Masyiah Rani Harusi, S.T., M.Eng</t>
+          <t>Dr.Eng. Ir. Muralia Hustim, S.T., M.T., IPM., AER</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution</t>
+          <t>Environmental Noise</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +933,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4479-9649</t>
+          <t>0000-0001-8323-1549</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6783007</t>
+          <t>5977747</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57217107296</t>
+          <t>55438107000</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Ir. Rasdiana Zakaria, S.T., M.T</t>
+          <t>Ir. Nurul Masyiah Rani Harusi, S.T., M.Eng</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Environmental Risk Management</t>
+          <t>Air Pollution</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -986,17 +982,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1534-8443</t>
+          <t>0000-0002-4479-9649</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6671275</t>
+          <t>6783007</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57201774235</t>
+          <t>57217107296</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,12 +1007,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ir. Zarah Arwieny Hanami, S.T., M.T</t>
+          <t>Ir. Rasdiana Zakaria, S.T., M.T</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1026,7 +1022,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution</t>
+          <t>Environmental Risk Management</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1035,17 +1031,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3439-8419</t>
+          <t>0000-0002-1534-8443</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6778717</t>
+          <t>6671275</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57201778090</t>
+          <t>57201774235</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1060,12 +1056,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr.Eng. Ir. Muhammad Isran Ramli, S.T., M.T., IPM., AER</t>
+          <t>Ir. Zarah Arwieny Hanami, S.T., M.T</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1075,7 +1071,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Environmental Transportation</t>
+          <t>Air Pollution</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1084,17 +1080,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5904-1358</t>
+          <t>0000-0003-3439-8419</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>5977376</t>
+          <t>6778717</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57194179510</t>
+          <t>57201778090</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1109,12 +1105,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Sumarni Hamid, MT.</t>
+          <t>Prof. Dr.Eng. Ir. Muhammad Isran Ramli, S.T., M.T., IPM., AER</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1133,17 +1129,17 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8328-1930</t>
+          <t>0000-0001-5904-1358</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>5977376</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>56720927100</t>
+          <t>57194179510</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1158,31 +1154,43 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Herni Halim</t>
+          <t>Prof. Dr. Sumarni Hamid, MT.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Universiti Sains Malaysia</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Environmental Noise</t>
+          <t>Environmental Transportation</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-8328-1930</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>21966</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>56720927100</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1195,22 +1203,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Sitti Asmah Hassan, PhD</t>
+          <t>Dr. Herni Halim</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Universiti Teknologi Malaysia</t>
+          <t>Universiti Sains Malaysia</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Transportation and Traffic Engineering</t>
+          <t>Environmental Noise</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1219,11 +1227,7 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>56355098100</t>
-        </is>
-      </c>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1236,22 +1240,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. Mitsuhiko Hata</t>
+          <t>Sitti Asmah Hassan, PhD</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Kanazawa University</t>
+          <t>Universiti Teknologi Malaysia</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Aerosol</t>
+          <t>Transportation and Traffic Engineering</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1262,7 +1266,7 @@
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>7203026498</t>
+          <t>56355098100</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1277,12 +1281,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Prof. Masami Furuuchi</t>
+          <t>Prof. Mitsuhiko Hata</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1292,7 +1296,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution Control Technology</t>
+          <t>Aerosol</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1303,7 +1307,7 @@
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>6603629476</t>
+          <t>7203026498</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1318,12 +1322,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr.Eng. Muhammad Amin</t>
+          <t>Prof. Masami Furuuchi</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1333,7 +1337,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Ambient and Personal Exposure of Particulate</t>
+          <t>Air Pollution Control Technology</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1344,7 +1348,7 @@
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>57223359290</t>
+          <t>6603629476</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1359,22 +1363,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Fachreza</t>
+          <t>Dr.Eng. Muhammad Amin</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Kanazawa University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution</t>
+          <t>Ambient and Personal Exposure of Particulate</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1383,7 +1387,11 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>57223359290</t>
+        </is>
+      </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1396,12 +1404,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Femy Wahyuny</t>
+          <t>Fachreza</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1411,7 +1419,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Traffic Noise</t>
+          <t>Air Pollution</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1431,10 +1439,26 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Femy Wahyuny</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Traffic Noise</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1442,7 +1466,11 @@
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1631,15 +1659,32 @@
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="12" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
